--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56823091</v>
+        <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>93201</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brånaknösarna, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610408</v>
+        <v>610518</v>
       </c>
       <c r="R2" t="n">
-        <v>7227482</v>
+        <v>7227378</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,41 +776,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823091</t>
+          <t>https://artportalen.se/Sighting/135818927</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56823087</v>
+        <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +812,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brånaknösarna, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610575</v>
+        <v>610603</v>
       </c>
       <c r="R3" t="n">
-        <v>7227477</v>
+        <v>7227252</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +871,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt på mycket fin silverved</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,41 +902,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823087</t>
+          <t>https://artportalen.se/Sighting/135818932</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56823089</v>
+        <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +938,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brånaknösarna, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610581</v>
+        <v>610592</v>
       </c>
       <c r="R4" t="n">
-        <v>7227509</v>
+        <v>7227259</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +997,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,41 +1023,35 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823089</t>
+          <t>https://artportalen.se/Sighting/135818933</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56823084</v>
+        <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79946</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1059,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610641</v>
+        <v>610612</v>
       </c>
       <c r="R5" t="n">
-        <v>7227388</v>
+        <v>7227229</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1113,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,41 +1139,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>silverstubbe/törvedsstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823084</t>
+          <t>https://artportalen.se/Sighting/135818937</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56823085</v>
+        <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>78334</v>
+        <v>91069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610631</v>
+        <v>610600</v>
       </c>
       <c r="R6" t="n">
-        <v>7227431</v>
+        <v>7227265</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,63 +1255,57 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>törvedsstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823085</t>
+          <t>https://artportalen.se/Sighting/135818931</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56823070</v>
+        <v>56823091</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610556</v>
+        <v>610408</v>
       </c>
       <c r="R7" t="n">
-        <v>7227287</v>
+        <v>7227482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1369,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1346,38 +1386,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823070</t>
+          <t>https://artportalen.se/Sighting/56823091</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56823088</v>
+        <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1427,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610575</v>
+        <v>610617</v>
       </c>
       <c r="R8" t="n">
-        <v>7227477</v>
+        <v>7227376</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,12 +1457,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,63 +1483,57 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823088</t>
+          <t>https://artportalen.se/Sighting/135818929</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56823090</v>
+        <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1543,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610581</v>
+        <v>610615</v>
       </c>
       <c r="R9" t="n">
-        <v>7227509</v>
+        <v>7227326</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,12 +1573,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,63 +1599,57 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56823090</t>
+          <t>https://artportalen.se/Sighting/135818930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56823086</v>
+        <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79917</v>
+        <v>79441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610631</v>
+        <v>610628</v>
       </c>
       <c r="R10" t="n">
-        <v>7227431</v>
+        <v>7227179</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,12 +1689,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,30 +1715,2503 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>törvedsstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818939</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>56823087</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>610575</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7227477</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823087</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56823089</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>610581</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7227509</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823089</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135818938</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>610632</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7227205</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818938</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>56823084</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>610641</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7227388</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>silverstubbe/törvedsstubbe</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823084</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135818928</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>610523</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7227383</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818928</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>56823085</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>610631</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7227431</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>törvedsstubbe</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823085</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135818918</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>610633</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7227125</v>
+      </c>
+      <c r="S17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818918</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135818919</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>610614</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7227157</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818919</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135818920</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>610589</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7227180</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på två granar och en tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818920</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135818921</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>610579</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7227186</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818921</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135818922</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>610547</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7227252</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack högt i gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818922</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135818923</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>610545</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7227264</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp i gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818923</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135818924</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>610503</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7227308</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack upp längs granstam</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818924</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135818925</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>610489</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7227322</v>
+      </c>
+      <c r="S24" t="n">
+        <v>26</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack. Granstam</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818925</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>56823070</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>610556</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7227287</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823070</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>56823088</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>610575</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7227477</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823088</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>56823090</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>610581</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7227509</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823090</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135818926</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>610484</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7227400</v>
+      </c>
+      <c r="S28" t="n">
+        <v>38</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818926</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135818935</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>610626</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7227261</v>
+      </c>
+      <c r="S29" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818935</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135818936</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>610614</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7227229</v>
+      </c>
+      <c r="S30" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135818936</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>56823086</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brånaknösarna, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>610631</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7227431</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>törvedsstubbe</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/56823086</t>
         </is>
@@ -1697,6 +4228,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135818938</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135818928</v>
       </c>
       <c r="B15" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135818918</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135818919</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135818920</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>135818921</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135818922</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135818923</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135818924</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>135818925</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135818926</v>
       </c>
       <c r="B28" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135818935</v>
       </c>
       <c r="B29" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135818936</v>
       </c>
       <c r="B30" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135818938</v>
       </c>
       <c r="B13" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135818928</v>
       </c>
       <c r="B15" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135818926</v>
       </c>
       <c r="B28" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135818935</v>
       </c>
       <c r="B29" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135818936</v>
       </c>
       <c r="B30" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135818938</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135818928</v>
       </c>
       <c r="B15" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135818918</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135818919</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135818920</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>135818921</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135818922</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135818923</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135818924</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>135818925</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135818926</v>
       </c>
       <c r="B28" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135818935</v>
       </c>
       <c r="B29" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135818936</v>
       </c>
       <c r="B30" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135818938</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135818928</v>
       </c>
       <c r="B15" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135818918</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135818919</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135818920</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>135818921</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135818922</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135818923</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135818924</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>135818925</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135818926</v>
       </c>
       <c r="B28" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135818935</v>
       </c>
       <c r="B29" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135818936</v>
       </c>
       <c r="B30" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30075-2026 artfynd.xlsx
+++ b/artfynd/A 30075-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135818927</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135818932</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135818933</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>135818937</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135818931</v>
       </c>
       <c r="B6" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135818929</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135818930</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135818939</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>135818938</v>
       </c>
       <c r="B13" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135818928</v>
       </c>
       <c r="B15" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135818918</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135818919</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135818920</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>135818921</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135818922</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>135818923</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135818924</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>135818925</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135818926</v>
       </c>
       <c r="B28" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>135818935</v>
       </c>
       <c r="B29" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>135818936</v>
       </c>
       <c r="B30" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
